--- a/docs/StructureDefinition-MedRefillRequestMHVProvenance-pat.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVProvenance-pat.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVProvenance-pat.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVProvenance-pat.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVProvenance-pat.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVProvenance-pat.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
